--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
@@ -79,24 +79,12 @@
     <t xml:space="preserve">Aysen</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11402</t>
   </si>
   <si>
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11303</t>
   </si>
   <si>
@@ -661,6 +649,12 @@
     <t xml:space="preserve">Quintero</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5404</t>
   </si>
   <si>
@@ -1309,6 +1303,12 @@
     <t xml:space="preserve">Canela</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">1404</t>
   </si>
   <si>
@@ -2062,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:25</t>
+    <t xml:space="preserve">2026-09-09 20:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2606,7 +2606,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46.57</v>
+        <v>45.05</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>16</v>
@@ -2638,7 +2638,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45.05</v>
+        <v>44.44</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>16</v>
@@ -2670,7 +2670,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>44.55</v>
+        <v>43.43</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
@@ -2702,7 +2702,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44.44</v>
+        <v>43.06</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
@@ -2713,10 +2713,10 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
@@ -2734,7 +2734,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>43.43</v>
+        <v>42.45</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2766,7 +2766,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>43.06</v>
+        <v>40.53</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2777,10 +2777,10 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -2798,7 +2798,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>42.45</v>
+        <v>40.17</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2809,10 +2809,10 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2830,7 +2830,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>40.53</v>
+        <v>37.13</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2841,10 +2841,10 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -2862,7 +2862,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>40.17</v>
+        <v>36.29</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2873,10 +2873,10 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2894,7 +2894,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37.13</v>
+        <v>33.33</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2905,28 +2905,28 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>36.29</v>
+        <v>74.68</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2937,28 +2937,28 @@
         <v>2024</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33.33</v>
+        <v>71</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -2972,25 +2972,25 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>74.68</v>
+        <v>70.2</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3004,7 +3004,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>49</v>
@@ -3013,16 +3013,16 @@
         <v>50</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>71</v>
+        <v>68.93</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3036,7 +3036,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>51</v>
@@ -3045,16 +3045,16 @@
         <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>70.2</v>
+        <v>66.15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3068,7 +3068,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>53</v>
@@ -3077,16 +3077,16 @@
         <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>68.93</v>
+        <v>63.53</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3097,28 +3097,28 @@
         <v>2024</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>66.15</v>
+        <v>58.27</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3129,28 +3129,28 @@
         <v>2024</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>63.53</v>
+        <v>57.8</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3161,28 +3161,28 @@
         <v>2024</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>58.27</v>
+        <v>57.34</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3193,28 +3193,28 @@
         <v>2024</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>57.8</v>
+        <v>55.37</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3225,28 +3225,28 @@
         <v>2024</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>57.34</v>
+        <v>54.46</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3257,10 +3257,10 @@
         <v>2024</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>68</v>
@@ -3269,16 +3269,16 @@
         <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>55.37</v>
+        <v>54.41</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3292,7 +3292,7 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3301,16 +3301,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>54.46</v>
+        <v>54.21</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3321,10 +3321,10 @@
         <v>2024</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3333,16 +3333,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>54.41</v>
+        <v>53.64</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3353,10 +3353,10 @@
         <v>2024</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3365,16 +3365,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>54.21</v>
+        <v>53.41</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3385,10 +3385,10 @@
         <v>2024</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3397,16 +3397,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>53.64</v>
+        <v>53.39</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3420,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3429,16 +3429,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>53.41</v>
+        <v>52.9</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3449,10 +3449,10 @@
         <v>2024</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3461,16 +3461,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>53.39</v>
+        <v>52.74</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3481,28 +3481,28 @@
         <v>2024</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>52.9</v>
+        <v>52.31</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3516,25 +3516,25 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>52.74</v>
+        <v>52.15</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3545,10 +3545,10 @@
         <v>2024</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>87</v>
@@ -3557,16 +3557,16 @@
         <v>88</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>52.31</v>
+        <v>51.9</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3577,10 +3577,10 @@
         <v>2024</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>89</v>
@@ -3589,16 +3589,16 @@
         <v>90</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>52.15</v>
+        <v>51.85</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3609,10 +3609,10 @@
         <v>2024</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>91</v>
@@ -3621,16 +3621,16 @@
         <v>92</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>51.9</v>
+        <v>51.81</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3641,10 +3641,10 @@
         <v>2024</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>93</v>
@@ -3653,16 +3653,16 @@
         <v>94</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>51.85</v>
+        <v>51.59</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3673,10 +3673,10 @@
         <v>2024</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>95</v>
@@ -3685,16 +3685,16 @@
         <v>96</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>51.81</v>
+        <v>51.37</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3705,10 +3705,10 @@
         <v>2024</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>97</v>
@@ -3717,16 +3717,16 @@
         <v>98</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>51.59</v>
+        <v>50.96</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3737,10 +3737,10 @@
         <v>2024</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>99</v>
@@ -3749,16 +3749,16 @@
         <v>100</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>51.37</v>
+        <v>50.74</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3769,10 +3769,10 @@
         <v>2024</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>101</v>
@@ -3781,16 +3781,16 @@
         <v>102</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>50.96</v>
+        <v>50.62</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3804,7 +3804,7 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>103</v>
@@ -3813,16 +3813,16 @@
         <v>104</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>50.74</v>
+        <v>50.13</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3833,10 +3833,10 @@
         <v>2024</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>105</v>
@@ -3845,16 +3845,16 @@
         <v>106</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>50.62</v>
+        <v>49.35</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3868,7 +3868,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>107</v>
@@ -3877,16 +3877,16 @@
         <v>108</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>50.13</v>
+        <v>49.29</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3897,10 +3897,10 @@
         <v>2024</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>109</v>
@@ -3909,16 +3909,16 @@
         <v>110</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>49.35</v>
+        <v>49.14</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3929,10 +3929,10 @@
         <v>2024</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -3941,16 +3941,16 @@
         <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>49.29</v>
+        <v>49.08</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3961,10 +3961,10 @@
         <v>2024</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>113</v>
@@ -3973,16 +3973,16 @@
         <v>114</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>49.14</v>
+        <v>49.06</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -3993,10 +3993,10 @@
         <v>2024</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>115</v>
@@ -4005,16 +4005,16 @@
         <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>49.08</v>
+        <v>49.04</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4025,10 +4025,10 @@
         <v>2024</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>117</v>
@@ -4037,16 +4037,16 @@
         <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>49.06</v>
+        <v>48.94</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4060,7 +4060,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>119</v>
@@ -4069,16 +4069,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>49.04</v>
+        <v>48.89</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4089,10 +4089,10 @@
         <v>2024</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -4101,16 +4101,16 @@
         <v>122</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>48.94</v>
+        <v>48.61</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4121,10 +4121,10 @@
         <v>2024</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>123</v>
@@ -4133,16 +4133,16 @@
         <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>48.89</v>
+        <v>48.6</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4153,10 +4153,10 @@
         <v>2024</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>125</v>
@@ -4165,16 +4165,16 @@
         <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>48.61</v>
+        <v>48.49</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4188,7 +4188,7 @@
         <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>127</v>
@@ -4197,16 +4197,16 @@
         <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>48.6</v>
+        <v>48.45</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4217,10 +4217,10 @@
         <v>2024</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>129</v>
@@ -4229,16 +4229,16 @@
         <v>130</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>48.49</v>
+        <v>48.4</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4249,10 +4249,10 @@
         <v>2024</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>131</v>
@@ -4261,16 +4261,16 @@
         <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>48.45</v>
+        <v>48.16</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4284,7 +4284,7 @@
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>133</v>
@@ -4293,16 +4293,16 @@
         <v>134</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="2" t="n">
         <v>48</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>48.4</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4316,7 +4316,7 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>135</v>
@@ -4325,16 +4325,16 @@
         <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>48.16</v>
+        <v>47.91</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4345,10 +4345,10 @@
         <v>2024</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>137</v>
@@ -4357,16 +4357,16 @@
         <v>138</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>48</v>
+        <v>47.74</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4377,10 +4377,10 @@
         <v>2024</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>139</v>
@@ -4389,16 +4389,16 @@
         <v>140</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>47.91</v>
+        <v>47.73</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4409,10 +4409,10 @@
         <v>2024</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
@@ -4421,16 +4421,16 @@
         <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>47.74</v>
+        <v>47.64</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4441,10 +4441,10 @@
         <v>2024</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>143</v>
@@ -4453,16 +4453,16 @@
         <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>47.73</v>
+        <v>47.61</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4473,10 +4473,10 @@
         <v>2024</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>145</v>
@@ -4485,16 +4485,16 @@
         <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>47.64</v>
+        <v>47.59</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4508,7 +4508,7 @@
         <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>147</v>
@@ -4517,16 +4517,16 @@
         <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>47.61</v>
+        <v>47.49</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4537,10 +4537,10 @@
         <v>2024</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>149</v>
@@ -4549,16 +4549,16 @@
         <v>150</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>47.59</v>
+        <v>47.46</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4569,10 +4569,10 @@
         <v>2024</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>151</v>
@@ -4581,16 +4581,16 @@
         <v>152</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>47.49</v>
+        <v>47.38</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4601,10 +4601,10 @@
         <v>2024</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>153</v>
@@ -4613,16 +4613,16 @@
         <v>154</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>47.46</v>
+        <v>47.37</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4633,10 +4633,10 @@
         <v>2024</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>155</v>
@@ -4645,16 +4645,16 @@
         <v>156</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>47.38</v>
+        <v>47.24</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4665,10 +4665,10 @@
         <v>2024</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>157</v>
@@ -4677,16 +4677,16 @@
         <v>158</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>47.37</v>
+        <v>47.19</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4700,7 +4700,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>159</v>
@@ -4709,16 +4709,16 @@
         <v>160</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>47.24</v>
+        <v>47.17</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4729,28 +4729,28 @@
         <v>2024</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>47.19</v>
+        <v>46.94</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4764,25 +4764,25 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>47.17</v>
+        <v>46.88</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4793,28 +4793,28 @@
         <v>2024</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46.94</v>
+        <v>46.85</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4825,10 +4825,10 @@
         <v>2024</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4837,16 +4837,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46.88</v>
+        <v>46.67</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4857,10 +4857,10 @@
         <v>2024</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4869,16 +4869,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46.85</v>
+        <v>46.66</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4889,10 +4889,10 @@
         <v>2024</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4901,16 +4901,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46.67</v>
+        <v>46.64</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4921,10 +4921,10 @@
         <v>2024</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4933,16 +4933,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46.66</v>
+        <v>46.59</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -4956,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4965,16 +4965,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46.64</v>
+        <v>46.46</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -4985,10 +4985,10 @@
         <v>2024</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -4997,16 +4997,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46.59</v>
+        <v>46.45</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5017,10 +5017,10 @@
         <v>2024</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5029,16 +5029,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46.46</v>
+        <v>46.44</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5049,10 +5049,10 @@
         <v>2024</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5061,16 +5061,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46.45</v>
+        <v>46.44</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5081,10 +5081,10 @@
         <v>2024</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5093,16 +5093,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46.44</v>
+        <v>46.32</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5125,16 +5125,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46.44</v>
+        <v>46.31</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5145,10 +5145,10 @@
         <v>2024</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5157,16 +5157,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46.32</v>
+        <v>46.14</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5177,10 +5177,10 @@
         <v>2024</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5189,16 +5189,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46.31</v>
+        <v>46.07</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5212,7 +5212,7 @@
         <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5221,16 +5221,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46.14</v>
+        <v>46.03</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5253,16 +5253,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46.07</v>
+        <v>45.98</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5273,10 +5273,10 @@
         <v>2024</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5285,16 +5285,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46.03</v>
+        <v>45.83</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5305,10 +5305,10 @@
         <v>2024</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5317,16 +5317,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45.98</v>
+        <v>45.82</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5337,10 +5337,10 @@
         <v>2024</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5349,16 +5349,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45.83</v>
+        <v>45.72</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5369,10 +5369,10 @@
         <v>2024</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5381,16 +5381,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45.82</v>
+        <v>45.7</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5404,7 +5404,7 @@
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5413,16 +5413,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45.72</v>
+        <v>45.66</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5433,10 +5433,10 @@
         <v>2024</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5445,16 +5445,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45.7</v>
+        <v>45.65</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5465,10 +5465,10 @@
         <v>2024</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5477,16 +5477,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45.66</v>
+        <v>45.29</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5497,10 +5497,10 @@
         <v>2024</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5509,16 +5509,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45.65</v>
+        <v>45.2</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5529,10 +5529,10 @@
         <v>2024</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5541,16 +5541,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45.29</v>
+        <v>45.02</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5564,7 +5564,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5573,16 +5573,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45.2</v>
+        <v>44.99</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5596,7 +5596,7 @@
         <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5605,16 +5605,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>44.99</v>
+        <v>44.98</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5625,10 +5625,10 @@
         <v>2024</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5637,10 +5637,10 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5657,10 +5657,10 @@
         <v>2024</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5669,16 +5669,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>44.98</v>
+        <v>44.85</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5689,10 +5689,10 @@
         <v>2024</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5701,16 +5701,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>44.85</v>
+        <v>44.84</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5721,10 +5721,10 @@
         <v>2024</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5733,16 +5733,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>44.84</v>
+        <v>44.78</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5753,10 +5753,10 @@
         <v>2024</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5765,16 +5765,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>44.78</v>
+        <v>44.7</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5785,10 +5785,10 @@
         <v>2024</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5797,16 +5797,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>44.7</v>
+        <v>44.67</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5817,10 +5817,10 @@
         <v>2024</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5829,16 +5829,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>44.67</v>
+        <v>44.62</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5849,10 +5849,10 @@
         <v>2024</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5861,16 +5861,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>44.62</v>
+        <v>44.48</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5881,10 +5881,10 @@
         <v>2024</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5893,10 +5893,10 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5913,10 +5913,10 @@
         <v>2024</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5925,16 +5925,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>44.48</v>
+        <v>44.39</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5945,10 +5945,10 @@
         <v>2024</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5957,16 +5957,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>44.39</v>
+        <v>44.33</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -5977,10 +5977,10 @@
         <v>2024</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -5989,16 +5989,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>44.33</v>
+        <v>44.3</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6009,10 +6009,10 @@
         <v>2024</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6021,16 +6021,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>44.3</v>
+        <v>44.19</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6041,10 +6041,10 @@
         <v>2024</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6053,16 +6053,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>44.19</v>
+        <v>44.13</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6073,10 +6073,10 @@
         <v>2024</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6085,16 +6085,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>44.13</v>
+        <v>44.06</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6105,10 +6105,10 @@
         <v>2024</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6117,16 +6117,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>44.06</v>
+        <v>44</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6140,7 +6140,7 @@
         <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6149,16 +6149,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>44</v>
+        <v>43.94</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6169,10 +6169,10 @@
         <v>2024</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6181,16 +6181,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>43.94</v>
+        <v>43.87</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6201,10 +6201,10 @@
         <v>2024</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6213,10 +6213,10 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6233,10 +6233,10 @@
         <v>2024</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6245,16 +6245,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>43.87</v>
+        <v>43.83</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6265,10 +6265,10 @@
         <v>2024</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6277,16 +6277,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>43.83</v>
+        <v>43.7</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6297,10 +6297,10 @@
         <v>2024</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6309,16 +6309,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>43.7</v>
+        <v>43.58</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6329,10 +6329,10 @@
         <v>2024</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6341,16 +6341,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>43.58</v>
+        <v>43.57</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6361,10 +6361,10 @@
         <v>2024</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6373,16 +6373,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>43.57</v>
+        <v>43.55</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6393,10 +6393,10 @@
         <v>2024</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6405,16 +6405,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>43.55</v>
+        <v>43.52</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6425,10 +6425,10 @@
         <v>2024</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6437,16 +6437,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>43.52</v>
+        <v>43.46</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6457,10 +6457,10 @@
         <v>2024</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6469,16 +6469,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>43.46</v>
+        <v>43.43</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6489,10 +6489,10 @@
         <v>2024</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6501,16 +6501,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>43.43</v>
+        <v>43.42</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6524,7 +6524,7 @@
         <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6533,16 +6533,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>43.42</v>
+        <v>43.39</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6556,7 +6556,7 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6565,16 +6565,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>43.39</v>
+        <v>43.38</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6588,7 +6588,7 @@
         <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6597,16 +6597,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6617,10 +6617,10 @@
         <v>2024</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6629,16 +6629,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>43.26</v>
+        <v>43.24</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6652,7 +6652,7 @@
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6661,16 +6661,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>43.24</v>
+        <v>43.17</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6684,7 +6684,7 @@
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6693,16 +6693,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>43.17</v>
+        <v>42.92</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6716,7 +6716,7 @@
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6725,16 +6725,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>42.92</v>
+        <v>42.85</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6745,10 +6745,10 @@
         <v>2024</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6757,16 +6757,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>42.85</v>
+        <v>42.75</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6777,10 +6777,10 @@
         <v>2024</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6789,16 +6789,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>42.75</v>
+        <v>42.73</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6809,10 +6809,10 @@
         <v>2024</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6821,16 +6821,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>42.73</v>
+        <v>42.68</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6841,10 +6841,10 @@
         <v>2024</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6853,16 +6853,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>42.68</v>
+        <v>42.65</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6873,10 +6873,10 @@
         <v>2024</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6885,16 +6885,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>42.65</v>
+        <v>42.63</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6905,10 +6905,10 @@
         <v>2024</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6917,16 +6917,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>42.63</v>
+        <v>42.6</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6937,10 +6937,10 @@
         <v>2024</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -6949,16 +6949,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>42.6</v>
+        <v>42.58</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -6969,10 +6969,10 @@
         <v>2024</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -6981,16 +6981,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>42.58</v>
+        <v>42.54</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7004,7 +7004,7 @@
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7013,16 +7013,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>42.54</v>
+        <v>42.46</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7036,7 +7036,7 @@
         <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7045,16 +7045,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>42.46</v>
+        <v>42.42</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7068,7 +7068,7 @@
         <v>7</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7077,16 +7077,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>42.42</v>
+        <v>42.34</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7097,10 +7097,10 @@
         <v>2024</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7109,16 +7109,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>42.34</v>
+        <v>42.26</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7129,10 +7129,10 @@
         <v>2024</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7141,16 +7141,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>42.26</v>
+        <v>42.14</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7161,10 +7161,10 @@
         <v>2024</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7173,16 +7173,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>42.14</v>
+        <v>42.02</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7193,10 +7193,10 @@
         <v>2024</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7205,16 +7205,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>42.02</v>
+        <v>41.78</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7225,10 +7225,10 @@
         <v>2024</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7237,16 +7237,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>41.78</v>
+        <v>41.77</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7257,10 +7257,10 @@
         <v>2024</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7269,16 +7269,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>41.77</v>
+        <v>41.73</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7289,10 +7289,10 @@
         <v>2024</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7301,16 +7301,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>41.73</v>
+        <v>41.72</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7324,7 +7324,7 @@
         <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7333,16 +7333,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>41.72</v>
+        <v>41.66</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7353,10 +7353,10 @@
         <v>2024</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7365,16 +7365,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>41.66</v>
+        <v>41.61</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7385,10 +7385,10 @@
         <v>2024</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7397,16 +7397,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>41.61</v>
+        <v>41.57</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7417,10 +7417,10 @@
         <v>2024</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7429,16 +7429,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>41.57</v>
+        <v>41.55</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7449,10 +7449,10 @@
         <v>2024</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7461,16 +7461,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>41.55</v>
+        <v>41.44</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7484,7 +7484,7 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7493,16 +7493,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>41.44</v>
+        <v>40.97</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7513,10 +7513,10 @@
         <v>2024</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7525,16 +7525,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>40.97</v>
+        <v>40.93</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7545,10 +7545,10 @@
         <v>2024</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7557,16 +7557,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>40.93</v>
+        <v>40.78</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7580,7 +7580,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7589,16 +7589,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>40.78</v>
+        <v>40.67</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7612,7 +7612,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7621,16 +7621,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>40.67</v>
+        <v>40.62</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7644,7 +7644,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7653,16 +7653,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>40.62</v>
+        <v>40.61</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7673,10 +7673,10 @@
         <v>2024</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7685,16 +7685,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>40.61</v>
+        <v>40.56</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7708,7 +7708,7 @@
         <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7717,16 +7717,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>40.56</v>
+        <v>40.53</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7737,10 +7737,10 @@
         <v>2024</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7749,16 +7749,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>40.53</v>
+        <v>40.52</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7769,10 +7769,10 @@
         <v>2024</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7781,16 +7781,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>40.52</v>
+        <v>40.41</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7804,7 +7804,7 @@
         <v>6</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7813,16 +7813,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>40.41</v>
+        <v>40.05</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7833,10 +7833,10 @@
         <v>2024</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7845,16 +7845,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>40.05</v>
+        <v>39.8</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7865,10 +7865,10 @@
         <v>2024</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7877,16 +7877,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>39.8</v>
+        <v>39.56</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7897,10 +7897,10 @@
         <v>2024</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7909,16 +7909,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>39.56</v>
+        <v>39.29</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7929,10 +7929,10 @@
         <v>2024</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -7941,16 +7941,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>39.29</v>
+        <v>39.07</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -7961,10 +7961,10 @@
         <v>2024</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -7973,16 +7973,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>39.07</v>
+        <v>38.98</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -7993,10 +7993,10 @@
         <v>2024</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8005,16 +8005,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>38.98</v>
+        <v>38.48</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8025,10 +8025,10 @@
         <v>2024</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8037,16 +8037,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>38.48</v>
+        <v>38.2</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8057,10 +8057,10 @@
         <v>2024</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8069,16 +8069,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>38.2</v>
+        <v>38.16</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8089,10 +8089,10 @@
         <v>2024</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8101,16 +8101,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>38.16</v>
+        <v>38.04</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8121,10 +8121,10 @@
         <v>2024</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8133,16 +8133,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>38.04</v>
+        <v>37.41</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8153,10 +8153,10 @@
         <v>2024</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8165,16 +8165,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>37.41</v>
+        <v>37.33</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8188,7 +8188,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8197,16 +8197,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>37.33</v>
+        <v>36.88</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8217,10 +8217,10 @@
         <v>2024</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8229,16 +8229,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>36.88</v>
+        <v>35.33</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8249,28 +8249,28 @@
         <v>2024</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>59</v>
+        <v>380</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>47</v>
+        <v>383</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>48</v>
+        <v>384</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>35.33</v>
+        <v>52.4</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8281,28 +8281,28 @@
         <v>2024</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D182" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="G182" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="F182" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>52.4</v>
+        <v>50.75</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8316,7 +8316,7 @@
         <v>3</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>388</v>
@@ -8325,16 +8325,16 @@
         <v>389</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>50.75</v>
+        <v>49.31</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8345,28 +8345,28 @@
         <v>2024</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>390</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>49.31</v>
+        <v>48.88</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8377,28 +8377,28 @@
         <v>2024</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>392</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>48.88</v>
+        <v>48.37</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8409,10 +8409,10 @@
         <v>2024</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>394</v>
@@ -8421,16 +8421,16 @@
         <v>395</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>48.37</v>
+        <v>48.35</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8441,28 +8441,28 @@
         <v>2024</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>396</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>48.35</v>
+        <v>48.1</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8473,28 +8473,28 @@
         <v>2024</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>398</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>48.1</v>
+        <v>47.37</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8508,7 +8508,7 @@
         <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>400</v>
@@ -8517,16 +8517,16 @@
         <v>401</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>47.37</v>
+        <v>47.22</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8537,10 +8537,10 @@
         <v>2024</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>402</v>
@@ -8549,16 +8549,16 @@
         <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>47.22</v>
+        <v>47.09</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8569,10 +8569,10 @@
         <v>2024</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>404</v>
@@ -8581,16 +8581,16 @@
         <v>405</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>47.09</v>
+        <v>46.53</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8601,10 +8601,10 @@
         <v>2024</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>406</v>
@@ -8613,16 +8613,16 @@
         <v>407</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>46.53</v>
+        <v>45.61</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8633,10 +8633,10 @@
         <v>2024</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>408</v>
@@ -8645,16 +8645,16 @@
         <v>409</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>45.61</v>
+        <v>45.59</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8665,10 +8665,10 @@
         <v>2024</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>410</v>
@@ -8677,16 +8677,16 @@
         <v>411</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>45.59</v>
+        <v>45.51</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8700,7 +8700,7 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>412</v>
@@ -8709,16 +8709,16 @@
         <v>413</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>45.51</v>
+        <v>45.39</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8732,7 +8732,7 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>414</v>
@@ -8741,16 +8741,16 @@
         <v>415</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>45.39</v>
+        <v>44.5</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8764,7 +8764,7 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>416</v>
@@ -8773,16 +8773,16 @@
         <v>417</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>44.5</v>
+        <v>43.89</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8793,10 +8793,10 @@
         <v>2024</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>418</v>
@@ -8805,16 +8805,16 @@
         <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>43.89</v>
+        <v>43.86</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8828,7 +8828,7 @@
         <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>420</v>
@@ -8837,16 +8837,16 @@
         <v>421</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>43.86</v>
+        <v>43.65</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8857,10 +8857,10 @@
         <v>2024</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>422</v>
@@ -8869,16 +8869,16 @@
         <v>423</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>43.65</v>
+        <v>42.58</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8889,10 +8889,10 @@
         <v>2024</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>424</v>
@@ -8901,16 +8901,16 @@
         <v>425</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>42.58</v>
+        <v>42.43</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8921,10 +8921,10 @@
         <v>2024</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>426</v>
@@ -8933,16 +8933,16 @@
         <v>427</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>42.43</v>
+        <v>41.82</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -8956,7 +8956,7 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>428</v>
@@ -8965,16 +8965,16 @@
         <v>429</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>41.82</v>
+        <v>41.74</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>430</v>
@@ -8997,10 +8997,10 @@
         <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9020,7 +9020,7 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>432</v>
@@ -9029,10 +9029,10 @@
         <v>433</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9052,7 +9052,7 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>434</v>
@@ -9061,10 +9061,10 @@
         <v>435</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9084,7 +9084,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>436</v>
@@ -9093,10 +9093,10 @@
         <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9116,7 +9116,7 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>438</v>
@@ -9125,10 +9125,10 @@
         <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9148,7 +9148,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>440</v>
@@ -9157,10 +9157,10 @@
         <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9180,7 +9180,7 @@
         <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>442</v>
@@ -9189,10 +9189,10 @@
         <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9212,7 +9212,7 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>444</v>
@@ -9221,10 +9221,10 @@
         <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9244,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9253,10 +9253,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9276,7 +9276,7 @@
         <v>3</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9285,10 +9285,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9308,7 +9308,7 @@
         <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9317,10 +9317,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9340,7 +9340,7 @@
         <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9349,10 +9349,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9372,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9381,10 +9381,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9404,7 +9404,7 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9413,10 +9413,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9436,7 +9436,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9445,10 +9445,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9468,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9477,10 +9477,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
@@ -2062,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:17</t>
+    <t xml:space="preserve">2026-09-18 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
@@ -2062,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:36</t>
+    <t xml:space="preserve">2026-09-24 00:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
